--- a/results_(stress_test)_original/cnn_evaluation(stress_test)_plv_origin.xlsx
+++ b/results_(stress_test)_original/cnn_evaluation(stress_test)_plv_origin.xlsx
@@ -7,8 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="nrr_0.5" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="nrr_0.75" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="nrn_62" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="nrn_32" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="nrn_16" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="nrn_8" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="nrn_4" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -463,16 +466,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>60.51080550098232</v>
+        <v>90.4424778761062</v>
       </c>
       <c r="C2" t="n">
-        <v>54.76974100311516</v>
+        <v>88.6640171572221</v>
       </c>
       <c r="D2" t="n">
-        <v>1.425050229299814</v>
+        <v>0.3434636705191224</v>
       </c>
       <c r="E2" t="n">
-        <v>60.51080550098232</v>
+        <v>90.4424778761062</v>
       </c>
     </row>
     <row r="3">
@@ -482,16 +485,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>44.69548133595285</v>
+        <v>95.92920353982301</v>
       </c>
       <c r="C3" t="n">
-        <v>37.37710580887733</v>
+        <v>95.80566559224759</v>
       </c>
       <c r="D3" t="n">
-        <v>2.975536100566387</v>
+        <v>0.1172023002665961</v>
       </c>
       <c r="E3" t="n">
-        <v>44.69548133595285</v>
+        <v>95.92920353982302</v>
       </c>
     </row>
     <row r="4">
@@ -501,16 +504,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>62.475442043222</v>
+        <v>88.64306784660766</v>
       </c>
       <c r="C4" t="n">
-        <v>62.30201507448928</v>
+        <v>87.54758775469114</v>
       </c>
       <c r="D4" t="n">
-        <v>1.053520187735558</v>
+        <v>0.3706524204438514</v>
       </c>
       <c r="E4" t="n">
-        <v>62.47544204322201</v>
+        <v>88.64306784660766</v>
       </c>
     </row>
     <row r="5">
@@ -520,16 +523,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48.52652259332024</v>
+        <v>91.09144542772862</v>
       </c>
       <c r="C5" t="n">
-        <v>47.07175358162361</v>
+        <v>91.19004487604585</v>
       </c>
       <c r="D5" t="n">
-        <v>1.537239164113998</v>
+        <v>0.243758152743491</v>
       </c>
       <c r="E5" t="n">
-        <v>48.52652259332024</v>
+        <v>91.09144542772862</v>
       </c>
     </row>
     <row r="6">
@@ -539,16 +542,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>62.27897838899803</v>
+        <v>95.57522123893804</v>
       </c>
       <c r="C6" t="n">
-        <v>58.57560195304858</v>
+        <v>95.490727709208</v>
       </c>
       <c r="D6" t="n">
-        <v>1.054641541093588</v>
+        <v>0.1413992417413586</v>
       </c>
       <c r="E6" t="n">
-        <v>62.27897838899804</v>
+        <v>95.57522123893804</v>
       </c>
     </row>
     <row r="7">
@@ -558,16 +561,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>47.15127701375246</v>
+        <v>93.39233038348083</v>
       </c>
       <c r="C7" t="n">
-        <v>44.51016009707741</v>
+        <v>93.23898315272677</v>
       </c>
       <c r="D7" t="n">
-        <v>1.530354931950569</v>
+        <v>0.181716487306403</v>
       </c>
       <c r="E7" t="n">
-        <v>47.15127701375246</v>
+        <v>93.39233038348083</v>
       </c>
     </row>
     <row r="8">
@@ -577,16 +580,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>62.08251473477407</v>
+        <v>95.01474926253687</v>
       </c>
       <c r="C8" t="n">
-        <v>60.92166055637222</v>
+        <v>94.85092308256714</v>
       </c>
       <c r="D8" t="n">
-        <v>1.44246117270086</v>
+        <v>0.1287952974470045</v>
       </c>
       <c r="E8" t="n">
-        <v>62.08251473477407</v>
+        <v>95.01474926253687</v>
       </c>
     </row>
     <row r="9">
@@ -596,16 +599,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>73.28094302554028</v>
+        <v>98.23008849557523</v>
       </c>
       <c r="C9" t="n">
-        <v>72.56920262668407</v>
+        <v>98.22062304218119</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8012986945686862</v>
+        <v>0.04513446296396069</v>
       </c>
       <c r="E9" t="n">
-        <v>73.28094302554028</v>
+        <v>98.23008849557523</v>
       </c>
     </row>
     <row r="10">
@@ -615,16 +618,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>81.33595284872298</v>
+        <v>98.31858407079646</v>
       </c>
       <c r="C10" t="n">
-        <v>80.97312041477781</v>
+        <v>98.29717514945668</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5469881426542997</v>
+        <v>0.04086909893095528</v>
       </c>
       <c r="E10" t="n">
-        <v>81.33595284872298</v>
+        <v>98.31858407079646</v>
       </c>
     </row>
     <row r="11">
@@ -634,16 +637,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>74.65618860510806</v>
+        <v>95.04424778761062</v>
       </c>
       <c r="C11" t="n">
-        <v>74.71393811760841</v>
+        <v>94.78377995448592</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7404828388243914</v>
+        <v>0.114361928866659</v>
       </c>
       <c r="E11" t="n">
-        <v>74.65618860510806</v>
+        <v>95.04424778761062</v>
       </c>
     </row>
     <row r="12">
@@ -653,16 +656,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>79.76424361493123</v>
+        <v>91.79941002949852</v>
       </c>
       <c r="C12" t="n">
-        <v>79.59951150963026</v>
+        <v>91.7639970363862</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6378060313872993</v>
+        <v>0.2257910027819738</v>
       </c>
       <c r="E12" t="n">
-        <v>79.76424361493125</v>
+        <v>91.79941002949852</v>
       </c>
     </row>
     <row r="13">
@@ -672,16 +675,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>65.32416502946955</v>
+        <v>96.01769911504425</v>
       </c>
       <c r="C13" t="n">
-        <v>65.71845633187375</v>
+        <v>95.90724086121259</v>
       </c>
       <c r="D13" t="n">
-        <v>1.217100226320326</v>
+        <v>0.1156978754737793</v>
       </c>
       <c r="E13" t="n">
-        <v>65.32416502946955</v>
+        <v>96.01769911504425</v>
       </c>
     </row>
     <row r="14">
@@ -691,16 +694,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>62.37721021611002</v>
+        <v>92.33038348082596</v>
       </c>
       <c r="C14" t="n">
-        <v>60.41378713394317</v>
+        <v>92.14602436884751</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9819141495972872</v>
+        <v>0.2444695876823971</v>
       </c>
       <c r="E14" t="n">
-        <v>62.37721021611002</v>
+        <v>92.33038348082596</v>
       </c>
     </row>
     <row r="15">
@@ -710,16 +713,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>53.43811394891945</v>
+        <v>92.03539823008849</v>
       </c>
       <c r="C15" t="n">
-        <v>47.5325317691774</v>
+        <v>91.99257800881641</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4997165389359</v>
+        <v>0.1992878262739396</v>
       </c>
       <c r="E15" t="n">
-        <v>53.43811394891945</v>
+        <v>92.03539823008849</v>
       </c>
     </row>
     <row r="16">
@@ -729,16 +732,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>50.78585461689588</v>
+        <v>92.94985250737463</v>
       </c>
       <c r="C16" t="n">
-        <v>43.07426303202231</v>
+        <v>92.88877152452436</v>
       </c>
       <c r="D16" t="n">
-        <v>1.646974068135023</v>
+        <v>0.1796515244505524</v>
       </c>
       <c r="E16" t="n">
-        <v>50.78585461689588</v>
+        <v>92.94985250737463</v>
       </c>
     </row>
     <row r="17">
@@ -748,16 +751,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>67.4852652259332</v>
+        <v>96.40117994100294</v>
       </c>
       <c r="C17" t="n">
-        <v>67.26385023281935</v>
+        <v>96.40175356112749</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9116617357358336</v>
+        <v>0.09423171705918018</v>
       </c>
       <c r="E17" t="n">
-        <v>67.4852652259332</v>
+        <v>96.40117994100294</v>
       </c>
     </row>
     <row r="18">
@@ -767,16 +770,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>69.25343811394892</v>
+        <v>95.10324483775811</v>
       </c>
       <c r="C18" t="n">
-        <v>68.72733933005215</v>
+        <v>94.81417636375193</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9290124420076609</v>
+        <v>0.1920523365637877</v>
       </c>
       <c r="E18" t="n">
-        <v>69.25343811394892</v>
+        <v>95.10324483775811</v>
       </c>
     </row>
     <row r="19">
@@ -786,16 +789,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>79.27308447937132</v>
+        <v>96.13569321533923</v>
       </c>
       <c r="C19" t="n">
-        <v>78.85428770987785</v>
+        <v>95.89476665642307</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6645785593427718</v>
+        <v>0.1245180681886268</v>
       </c>
       <c r="E19" t="n">
-        <v>79.27308447937132</v>
+        <v>96.13569321533923</v>
       </c>
     </row>
     <row r="20">
@@ -805,16 +808,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>65.81532416502947</v>
+        <v>90.67846607669617</v>
       </c>
       <c r="C20" t="n">
-        <v>65.70397103257696</v>
+        <v>89.87649020572212</v>
       </c>
       <c r="D20" t="n">
-        <v>1.341991684399545</v>
+        <v>0.2634370588453142</v>
       </c>
       <c r="E20" t="n">
-        <v>65.81532416502947</v>
+        <v>90.67846607669617</v>
       </c>
     </row>
     <row r="21">
@@ -824,16 +827,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>55.10805500982318</v>
+        <v>88.05309734513274</v>
       </c>
       <c r="C21" t="n">
-        <v>54.66129311176531</v>
+        <v>87.66192175420565</v>
       </c>
       <c r="D21" t="n">
-        <v>1.936801292002201</v>
+        <v>0.2717842186582857</v>
       </c>
       <c r="E21" t="n">
-        <v>55.10805500982319</v>
+        <v>88.05309734513274</v>
       </c>
     </row>
     <row r="22">
@@ -843,16 +846,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>54.12573673870334</v>
+        <v>94.86725663716814</v>
       </c>
       <c r="C22" t="n">
-        <v>48.17469206817552</v>
+        <v>94.4231254698676</v>
       </c>
       <c r="D22" t="n">
-        <v>2.087357960641384</v>
+        <v>0.1305473278566448</v>
       </c>
       <c r="E22" t="n">
-        <v>54.12573673870335</v>
+        <v>94.86725663716814</v>
       </c>
     </row>
     <row r="23">
@@ -862,16 +865,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>55.79567779960707</v>
+        <v>90.8259587020649</v>
       </c>
       <c r="C23" t="n">
-        <v>51.95244377113863</v>
+        <v>90.14060668302065</v>
       </c>
       <c r="D23" t="n">
-        <v>1.565084643661976</v>
+        <v>0.2680365543172229</v>
       </c>
       <c r="E23" t="n">
-        <v>55.79567779960707</v>
+        <v>90.8259587020649</v>
       </c>
     </row>
     <row r="24">
@@ -881,16 +884,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>65.32416502946955</v>
+        <v>94.10064100900527</v>
       </c>
       <c r="C24" t="n">
-        <v>62.13763775872275</v>
+        <v>94.10206260973463</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9532034853473306</v>
+        <v>0.1431229623759161</v>
       </c>
       <c r="E24" t="n">
-        <v>65.32416502946955</v>
+        <v>94.10064100900527</v>
       </c>
     </row>
     <row r="25">
@@ -900,16 +903,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>54.81335952848723</v>
+        <v>94.07079646017698</v>
       </c>
       <c r="C25" t="n">
-        <v>53.98804955669411</v>
+        <v>93.93290569098178</v>
       </c>
       <c r="D25" t="n">
-        <v>1.452234588563442</v>
+        <v>0.2006784709480901</v>
       </c>
       <c r="E25" t="n">
-        <v>54.81335952848723</v>
+        <v>94.07079646017699</v>
       </c>
     </row>
     <row r="26">
@@ -919,16 +922,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>56.67976424361493</v>
+        <v>92.35988200589971</v>
       </c>
       <c r="C26" t="n">
-        <v>56.73763828876236</v>
+        <v>91.94718883753384</v>
       </c>
       <c r="D26" t="n">
-        <v>1.585975140333176</v>
+        <v>0.1779977315813388</v>
       </c>
       <c r="E26" t="n">
-        <v>56.67976424361493</v>
+        <v>92.35988200589971</v>
       </c>
     </row>
     <row r="27">
@@ -938,16 +941,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>49.11591355599214</v>
+        <v>84.98525073746313</v>
       </c>
       <c r="C27" t="n">
-        <v>48.57490499980857</v>
+        <v>83.70383116985616</v>
       </c>
       <c r="D27" t="n">
-        <v>1.491869773715734</v>
+        <v>0.5732573438535231</v>
       </c>
       <c r="E27" t="n">
-        <v>49.11591355599214</v>
+        <v>84.98525073746313</v>
       </c>
     </row>
     <row r="28">
@@ -957,16 +960,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>65.22593320235757</v>
+        <v>86.4896755162242</v>
       </c>
       <c r="C28" t="n">
-        <v>64.44220966824278</v>
+        <v>85.31133070793236</v>
       </c>
       <c r="D28" t="n">
-        <v>0.8468409702181816</v>
+        <v>0.3962775778636569</v>
       </c>
       <c r="E28" t="n">
-        <v>65.22593320235757</v>
+        <v>86.4896755162242</v>
       </c>
     </row>
     <row r="29">
@@ -976,16 +979,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>85.26522593320236</v>
+        <v>98.40707964601771</v>
       </c>
       <c r="C29" t="n">
-        <v>85.27646199036289</v>
+        <v>98.40856174619481</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4927291623316705</v>
+        <v>0.0541561868297246</v>
       </c>
       <c r="E29" t="n">
-        <v>85.26522593320236</v>
+        <v>98.40707964601771</v>
       </c>
     </row>
     <row r="30">
@@ -995,16 +998,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>64.3418467583497</v>
+        <v>98.37758112094396</v>
       </c>
       <c r="C30" t="n">
-        <v>60.91501195863761</v>
+        <v>98.40381138939443</v>
       </c>
       <c r="D30" t="n">
-        <v>1.202251293812878</v>
+        <v>0.04191444609628452</v>
       </c>
       <c r="E30" t="n">
-        <v>64.3418467583497</v>
+        <v>98.37758112094396</v>
       </c>
     </row>
     <row r="31">
@@ -1014,16 +1017,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>84.97053045186641</v>
+        <v>98.84955752212389</v>
       </c>
       <c r="C31" t="n">
-        <v>84.78874806405882</v>
+        <v>98.84146773635939</v>
       </c>
       <c r="D31" t="n">
-        <v>0.463767776847817</v>
+        <v>0.03980883152837222</v>
       </c>
       <c r="E31" t="n">
-        <v>84.9705304518664</v>
+        <v>98.84955752212389</v>
       </c>
     </row>
     <row r="32">
@@ -1033,16 +1036,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>63.3759004584152</v>
+        <v>93.55065066883508</v>
       </c>
       <c r="C32" t="n">
-        <v>61.41071295173388</v>
+        <v>93.22173799509083</v>
       </c>
       <c r="D32" t="n">
-        <v>1.233881484228186</v>
+        <v>0.1888023903486005</v>
       </c>
       <c r="E32" t="n">
-        <v>63.3759004584152</v>
+        <v>93.55065066883508</v>
       </c>
     </row>
     <row r="33">
@@ -1052,16 +1055,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>11.13517688156525</v>
+        <v>3.544496275822628</v>
       </c>
       <c r="C33" t="n">
-        <v>12.61464872958598</v>
+        <v>3.877808098377264</v>
       </c>
       <c r="D33" t="n">
-        <v>0.5290154307999746</v>
+        <v>0.1182399836064657</v>
       </c>
       <c r="E33" t="n">
-        <v>11.13517688156525</v>
+        <v>3.544496275822629</v>
       </c>
     </row>
   </sheetData>
@@ -1112,16 +1115,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>60.80550098231827</v>
+        <v>88.99705014749262</v>
       </c>
       <c r="C2" t="n">
-        <v>52.7663411156101</v>
+        <v>87.24117042636809</v>
       </c>
       <c r="D2" t="n">
-        <v>1.417591328732669</v>
+        <v>0.4100367680521838</v>
       </c>
       <c r="E2" t="n">
-        <v>60.80550098231827</v>
+        <v>88.99705014749262</v>
       </c>
     </row>
     <row r="3">
@@ -1131,16 +1134,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>50.09823182711198</v>
+        <v>94.92625368731564</v>
       </c>
       <c r="C3" t="n">
-        <v>47.36119833507499</v>
+        <v>94.71431023355532</v>
       </c>
       <c r="D3" t="n">
-        <v>1.715315774083138</v>
+        <v>0.1581096755827578</v>
       </c>
       <c r="E3" t="n">
-        <v>50.098231827112</v>
+        <v>94.92625368731564</v>
       </c>
     </row>
     <row r="4">
@@ -1150,16 +1153,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>74.26326129666012</v>
+        <v>88.34808259587021</v>
       </c>
       <c r="C4" t="n">
-        <v>73.82823192997091</v>
+        <v>87.10720841544614</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6746275573968887</v>
+        <v>0.3853665100973255</v>
       </c>
       <c r="E4" t="n">
-        <v>74.26326129666012</v>
+        <v>88.34808259587021</v>
       </c>
     </row>
     <row r="5">
@@ -1169,16 +1172,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>51.47347740667976</v>
+        <v>90.41315236290971</v>
       </c>
       <c r="C5" t="n">
-        <v>51.91356113935898</v>
+        <v>90.44699525281371</v>
       </c>
       <c r="D5" t="n">
-        <v>1.376499250531197</v>
+        <v>0.2801260213794497</v>
       </c>
       <c r="E5" t="n">
-        <v>51.47347740667977</v>
+        <v>90.41315236290971</v>
       </c>
     </row>
     <row r="6">
@@ -1188,16 +1191,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>70.23575638506877</v>
+        <v>95.36873156342183</v>
       </c>
       <c r="C6" t="n">
-        <v>68.53212178822547</v>
+        <v>95.2220328959605</v>
       </c>
       <c r="D6" t="n">
-        <v>0.765954714268446</v>
+        <v>0.1648998943914194</v>
       </c>
       <c r="E6" t="n">
-        <v>70.23575638506875</v>
+        <v>95.36873156342183</v>
       </c>
     </row>
     <row r="7">
@@ -1207,16 +1210,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>43.61493123772102</v>
+        <v>91.71091445427729</v>
       </c>
       <c r="C7" t="n">
-        <v>43.30278094102005</v>
+        <v>91.4767533921888</v>
       </c>
       <c r="D7" t="n">
-        <v>2.06546525657177</v>
+        <v>0.2072723241222169</v>
       </c>
       <c r="E7" t="n">
-        <v>43.61493123772102</v>
+        <v>91.71091445427729</v>
       </c>
     </row>
     <row r="8">
@@ -1226,16 +1229,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>65.42239685658153</v>
+        <v>92.38938053097345</v>
       </c>
       <c r="C8" t="n">
-        <v>63.83132075357224</v>
+        <v>92.10752414675449</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9953582580201328</v>
+        <v>0.1847415211688106</v>
       </c>
       <c r="E8" t="n">
-        <v>65.42239685658153</v>
+        <v>92.38938053097345</v>
       </c>
     </row>
     <row r="9">
@@ -1245,16 +1248,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>72.29862475442043</v>
+        <v>98.11209439528024</v>
       </c>
       <c r="C9" t="n">
-        <v>71.65037812560654</v>
+        <v>98.10599741968056</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6420378475449979</v>
+        <v>0.04092710632852459</v>
       </c>
       <c r="E9" t="n">
-        <v>72.29862475442044</v>
+        <v>98.11209439528024</v>
       </c>
     </row>
     <row r="10">
@@ -1264,16 +1267,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>82.80943025540275</v>
+        <v>97.34513274336283</v>
       </c>
       <c r="C10" t="n">
-        <v>82.66144053254585</v>
+        <v>97.29123328544908</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4241666593588889</v>
+        <v>0.07036300115764789</v>
       </c>
       <c r="E10" t="n">
-        <v>82.80943025540275</v>
+        <v>97.34513274336283</v>
       </c>
     </row>
     <row r="11">
@@ -1283,16 +1286,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>79.17485265225933</v>
+        <v>96.25368731563421</v>
       </c>
       <c r="C11" t="n">
-        <v>79.21273177367706</v>
+        <v>96.26641464817263</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6580823403783143</v>
+        <v>0.106218641977163</v>
       </c>
       <c r="E11" t="n">
-        <v>79.17485265225933</v>
+        <v>96.25368731563421</v>
       </c>
     </row>
     <row r="12">
@@ -1302,16 +1305,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>81.13948919449902</v>
+        <v>89.91150442477877</v>
       </c>
       <c r="C12" t="n">
-        <v>80.79638870901219</v>
+        <v>89.15431123038215</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7161783367628232</v>
+        <v>0.3208674600934198</v>
       </c>
       <c r="E12" t="n">
-        <v>81.13948919449902</v>
+        <v>89.91150442477877</v>
       </c>
     </row>
     <row r="13">
@@ -1321,16 +1324,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>68.17288801571709</v>
+        <v>93.6283185840708</v>
       </c>
       <c r="C13" t="n">
-        <v>68.0259510477551</v>
+        <v>93.08261231959698</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9818671774119139</v>
+        <v>0.2023443938116543</v>
       </c>
       <c r="E13" t="n">
-        <v>68.17288801571709</v>
+        <v>93.6283185840708</v>
       </c>
     </row>
     <row r="14">
@@ -1340,16 +1343,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>60.51080550098232</v>
+        <v>87.96460176991151</v>
       </c>
       <c r="C14" t="n">
-        <v>57.99284573125172</v>
+        <v>86.78064584085979</v>
       </c>
       <c r="D14" t="n">
-        <v>1.139046240597963</v>
+        <v>0.3878626045392594</v>
       </c>
       <c r="E14" t="n">
-        <v>60.51080550098232</v>
+        <v>87.96460176991151</v>
       </c>
     </row>
     <row r="15">
@@ -1359,16 +1362,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>51.47347740667976</v>
+        <v>89.20353982300885</v>
       </c>
       <c r="C15" t="n">
-        <v>43.57931496769103</v>
+        <v>88.87517737423029</v>
       </c>
       <c r="D15" t="n">
-        <v>1.495057728141546</v>
+        <v>0.2578186068877888</v>
       </c>
       <c r="E15" t="n">
-        <v>51.47347740667977</v>
+        <v>89.20353982300885</v>
       </c>
     </row>
     <row r="16">
@@ -1378,16 +1381,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>48.52652259332024</v>
+        <v>90.29498525073747</v>
       </c>
       <c r="C16" t="n">
-        <v>40.51883415460083</v>
+        <v>90.02888972228395</v>
       </c>
       <c r="D16" t="n">
-        <v>1.897647596895695</v>
+        <v>0.2735740392759908</v>
       </c>
       <c r="E16" t="n">
-        <v>48.52652259332024</v>
+        <v>90.29498525073745</v>
       </c>
     </row>
     <row r="17">
@@ -1397,16 +1400,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>70.92337917485266</v>
+        <v>93.68731563421829</v>
       </c>
       <c r="C17" t="n">
-        <v>71.10574486406611</v>
+        <v>93.59039152273107</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8232343643903732</v>
+        <v>0.1665061639255024</v>
       </c>
       <c r="E17" t="n">
-        <v>70.92337917485266</v>
+        <v>93.68731563421829</v>
       </c>
     </row>
     <row r="18">
@@ -1416,16 +1419,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>69.74459724950884</v>
+        <v>94.57244439830795</v>
       </c>
       <c r="C18" t="n">
-        <v>69.05602459237159</v>
+        <v>94.31842869531664</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9673197828233242</v>
+        <v>0.1843454861382649</v>
       </c>
       <c r="E18" t="n">
-        <v>69.74459724950884</v>
+        <v>94.57244439830795</v>
       </c>
     </row>
     <row r="19">
@@ -1435,16 +1438,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>85.46168958742632</v>
+        <v>95.63421828908555</v>
       </c>
       <c r="C19" t="n">
-        <v>85.40368843145593</v>
+        <v>95.17530264596495</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4416745228663785</v>
+        <v>0.1515011446939752</v>
       </c>
       <c r="E19" t="n">
-        <v>85.46168958742632</v>
+        <v>95.63421828908555</v>
       </c>
     </row>
     <row r="20">
@@ -1454,16 +1457,16 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>71.31630648330059</v>
+        <v>91.79941002949852</v>
       </c>
       <c r="C20" t="n">
-        <v>71.20691158722504</v>
+        <v>91.32048301894926</v>
       </c>
       <c r="D20" t="n">
-        <v>1.007916191592813</v>
+        <v>0.2557522364923595</v>
       </c>
       <c r="E20" t="n">
-        <v>71.31630648330058</v>
+        <v>91.79941002949852</v>
       </c>
     </row>
     <row r="21">
@@ -1473,16 +1476,16 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>58.05500982318271</v>
+        <v>87.05014749262537</v>
       </c>
       <c r="C21" t="n">
-        <v>57.93992581075295</v>
+        <v>86.02081737616325</v>
       </c>
       <c r="D21" t="n">
-        <v>1.905210334807634</v>
+        <v>0.341375049120567</v>
       </c>
       <c r="E21" t="n">
-        <v>58.05500982318271</v>
+        <v>87.05014749262537</v>
       </c>
     </row>
     <row r="22">
@@ -1492,16 +1495,16 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>59.33202357563851</v>
+        <v>92.50737463126843</v>
       </c>
       <c r="C22" t="n">
-        <v>54.2010824870428</v>
+        <v>92.22558079370532</v>
       </c>
       <c r="D22" t="n">
-        <v>1.519082257524133</v>
+        <v>0.1942990337003721</v>
       </c>
       <c r="E22" t="n">
-        <v>59.3320235756385</v>
+        <v>92.50737463126843</v>
       </c>
     </row>
     <row r="23">
@@ -1511,16 +1514,16 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>48.62475442043222</v>
+        <v>92.65486725663717</v>
       </c>
       <c r="C23" t="n">
-        <v>38.7964543321056</v>
+        <v>92.84784674056776</v>
       </c>
       <c r="D23" t="n">
-        <v>2.731718122959137</v>
+        <v>0.1947582047633963</v>
       </c>
       <c r="E23" t="n">
-        <v>48.62475442043222</v>
+        <v>92.65486725663717</v>
       </c>
     </row>
     <row r="24">
@@ -1530,16 +1533,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>80.6483300589391</v>
+        <v>93.30383480825958</v>
       </c>
       <c r="C24" t="n">
-        <v>80.69822803468807</v>
+        <v>93.04891093483916</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4999723993241787</v>
+        <v>0.1893620524733706</v>
       </c>
       <c r="E24" t="n">
-        <v>80.6483300589391</v>
+        <v>93.30383480825958</v>
       </c>
     </row>
     <row r="25">
@@ -1549,16 +1552,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>61.59135559921415</v>
+        <v>92.71386430678466</v>
       </c>
       <c r="C25" t="n">
-        <v>60.79357536786542</v>
+        <v>92.52878890899564</v>
       </c>
       <c r="D25" t="n">
-        <v>1.150459300726652</v>
+        <v>0.2690209590791103</v>
       </c>
       <c r="E25" t="n">
-        <v>61.59135559921415</v>
+        <v>92.71386430678466</v>
       </c>
     </row>
     <row r="26">
@@ -1568,16 +1571,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>57.07269155206287</v>
+        <v>91.09161843960588</v>
       </c>
       <c r="C26" t="n">
-        <v>56.34444133395943</v>
+        <v>90.92237083794254</v>
       </c>
       <c r="D26" t="n">
-        <v>1.711870610713959</v>
+        <v>0.2245141119471858</v>
       </c>
       <c r="E26" t="n">
-        <v>57.07269155206287</v>
+        <v>91.09161843960588</v>
       </c>
     </row>
     <row r="27">
@@ -1587,16 +1590,16 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>59.03732809430255</v>
+        <v>82.74336283185841</v>
       </c>
       <c r="C27" t="n">
-        <v>58.20664474536719</v>
+        <v>82.27815378015281</v>
       </c>
       <c r="D27" t="n">
-        <v>1.229286201298237</v>
+        <v>0.6248369453193543</v>
       </c>
       <c r="E27" t="n">
-        <v>59.03732809430255</v>
+        <v>82.74336283185841</v>
       </c>
     </row>
     <row r="28">
@@ -1606,16 +1609,16 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>59.03732809430255</v>
+        <v>86.10619469026548</v>
       </c>
       <c r="C28" t="n">
-        <v>59.03913994754441</v>
+        <v>84.76335278775548</v>
       </c>
       <c r="D28" t="n">
-        <v>1.063055321574211</v>
+        <v>0.5295894651125612</v>
       </c>
       <c r="E28" t="n">
-        <v>59.03732809430255</v>
+        <v>86.10619469026548</v>
       </c>
     </row>
     <row r="29">
@@ -1625,16 +1628,16 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>85.95284872298625</v>
+        <v>97.87610619469027</v>
       </c>
       <c r="C29" t="n">
-        <v>85.99141748486463</v>
+        <v>97.87667846930543</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4469227168010548</v>
+        <v>0.07296202907617347</v>
       </c>
       <c r="E29" t="n">
-        <v>85.95284872298625</v>
+        <v>97.87610619469027</v>
       </c>
     </row>
     <row r="30">
@@ -1644,16 +1647,16 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>72.49508840864441</v>
+        <v>96.22418879056048</v>
       </c>
       <c r="C30" t="n">
-        <v>71.14872743966671</v>
+        <v>96.32529479334421</v>
       </c>
       <c r="D30" t="n">
-        <v>0.7855809903849149</v>
+        <v>0.09042398333063867</v>
       </c>
       <c r="E30" t="n">
-        <v>72.49508840864441</v>
+        <v>96.22418879056048</v>
       </c>
     </row>
     <row r="31">
@@ -1663,16 +1666,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>88.21218074656188</v>
+        <v>95.63421828908555</v>
       </c>
       <c r="C31" t="n">
-        <v>88.09019182306744</v>
+        <v>95.49731226106104</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4555643675848842</v>
+        <v>0.124956238831021</v>
       </c>
       <c r="E31" t="n">
-        <v>88.21218074656188</v>
+        <v>95.63421828908555</v>
       </c>
     </row>
     <row r="32">
@@ -1682,16 +1685,16 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>66.25081859855928</v>
+        <v>92.2822198577266</v>
       </c>
       <c r="C32" t="n">
-        <v>64.46652131090053</v>
+        <v>91.88803300568458</v>
       </c>
       <c r="D32" t="n">
-        <v>1.123458785068942</v>
+        <v>0.2354910557623155</v>
       </c>
       <c r="E32" t="n">
-        <v>66.25081859855928</v>
+        <v>92.2822198577266</v>
       </c>
     </row>
     <row r="33">
@@ -1701,16 +1704,1963 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>12.31793906289482</v>
+        <v>3.640571601682856</v>
       </c>
       <c r="C33" t="n">
-        <v>14.0287247975542</v>
+        <v>3.958822654945838</v>
       </c>
       <c r="D33" t="n">
-        <v>0.5570813171290456</v>
+        <v>0.1310462059556206</v>
       </c>
       <c r="E33" t="n">
-        <v>12.31793906289482</v>
+        <v>3.640571601682856</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>f1_score</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>sub6ex1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>89.49852507374632</v>
+      </c>
+      <c r="C2" t="n">
+        <v>88.09279170708709</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3668104575520071</v>
+      </c>
+      <c r="E2" t="n">
+        <v>89.49852507374631</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sub6ex2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>93.42182890855457</v>
+      </c>
+      <c r="C3" t="n">
+        <v>93.13904184333566</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.2096607044572011</v>
+      </c>
+      <c r="E3" t="n">
+        <v>93.42182890855457</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sub6ex3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>88.8792290590749</v>
+      </c>
+      <c r="C4" t="n">
+        <v>87.7615224877884</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.3564662990781168</v>
+      </c>
+      <c r="E4" t="n">
+        <v>88.8792290590749</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sub7ex1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>89.11504424778761</v>
+      </c>
+      <c r="C5" t="n">
+        <v>89.07258020374901</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2974330407994178</v>
+      </c>
+      <c r="E5" t="n">
+        <v>89.11504424778761</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sub7ex2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>93.1268436578171</v>
+      </c>
+      <c r="C6" t="n">
+        <v>92.9898662824247</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1855994084685032</v>
+      </c>
+      <c r="E6" t="n">
+        <v>93.1268436578171</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sub7ex3</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>87.59202069222053</v>
+      </c>
+      <c r="C7" t="n">
+        <v>87.50714499646395</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3156393884060283</v>
+      </c>
+      <c r="E7" t="n">
+        <v>87.59202069222053</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sub8ex1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>92.50737463126843</v>
+      </c>
+      <c r="C8" t="n">
+        <v>92.13659592076657</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.2139128410872218</v>
+      </c>
+      <c r="E8" t="n">
+        <v>92.50737463126843</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sub8ex2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>96.34218289085545</v>
+      </c>
+      <c r="C9" t="n">
+        <v>96.30709544547352</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.08815529832584919</v>
+      </c>
+      <c r="E9" t="n">
+        <v>96.34218289085545</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sub8ex3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>95.6047197640118</v>
+      </c>
+      <c r="C10" t="n">
+        <v>95.61678305656679</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1105548150154694</v>
+      </c>
+      <c r="E10" t="n">
+        <v>95.60471976401179</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sub9ex1</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>94.27728613569322</v>
+      </c>
+      <c r="C11" t="n">
+        <v>94.32131084288035</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.1458359392531141</v>
+      </c>
+      <c r="E11" t="n">
+        <v>94.27728613569322</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sub9ex2</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>86.75516224188792</v>
+      </c>
+      <c r="C12" t="n">
+        <v>85.46675534221035</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.4794458400181611</v>
+      </c>
+      <c r="E12" t="n">
+        <v>86.7551622418879</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sub9ex3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>89.48477062950371</v>
+      </c>
+      <c r="C13" t="n">
+        <v>89.13584441858099</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.2930215361450488</v>
+      </c>
+      <c r="E13" t="n">
+        <v>89.48477062950371</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sub10ex1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>87.61061946902655</v>
+      </c>
+      <c r="C14" t="n">
+        <v>86.77541039544884</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.3908664526204423</v>
+      </c>
+      <c r="E14" t="n">
+        <v>87.61061946902655</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sub10ex2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>89.14454277286136</v>
+      </c>
+      <c r="C15" t="n">
+        <v>88.78693802914216</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.2796557291604889</v>
+      </c>
+      <c r="E15" t="n">
+        <v>89.14454277286136</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sub10ex3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>88.05309734513274</v>
+      </c>
+      <c r="C16" t="n">
+        <v>87.88634481920191</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.3108993948932038</v>
+      </c>
+      <c r="E16" t="n">
+        <v>88.05309734513274</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>sub11ex1</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>92.44837758112094</v>
+      </c>
+      <c r="C17" t="n">
+        <v>92.32178892880954</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.2081472873879344</v>
+      </c>
+      <c r="E17" t="n">
+        <v>92.44837758112094</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sub11ex2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>91.95243903493974</v>
+      </c>
+      <c r="C18" t="n">
+        <v>91.82342387554445</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.2681141650478973</v>
+      </c>
+      <c r="E18" t="n">
+        <v>91.95243903493974</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>sub11ex3</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>95.39823008849558</v>
+      </c>
+      <c r="C19" t="n">
+        <v>94.99245614633557</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.153077467912711</v>
+      </c>
+      <c r="E19" t="n">
+        <v>95.39823008849558</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>sub12ex1</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>88.08259587020649</v>
+      </c>
+      <c r="C20" t="n">
+        <v>87.03906206630353</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.462430155473218</v>
+      </c>
+      <c r="E20" t="n">
+        <v>88.08259587020649</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>sub12ex2</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>87.64011799410029</v>
+      </c>
+      <c r="C21" t="n">
+        <v>86.12852420107376</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.4061685600487787</v>
+      </c>
+      <c r="E21" t="n">
+        <v>87.64011799410029</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sub12ex3</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>90.08849557522123</v>
+      </c>
+      <c r="C22" t="n">
+        <v>88.8142898567624</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.3789399278789157</v>
+      </c>
+      <c r="E22" t="n">
+        <v>90.08849557522123</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>sub13ex1</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>89.08554572271387</v>
+      </c>
+      <c r="C23" t="n">
+        <v>89.15402095474204</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.2909904813452158</v>
+      </c>
+      <c r="E23" t="n">
+        <v>89.08554572271386</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sub13ex2</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>93.00884955752213</v>
+      </c>
+      <c r="C24" t="n">
+        <v>92.99047517095235</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.190801577298771</v>
+      </c>
+      <c r="E24" t="n">
+        <v>93.00884955752213</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sub13ex3</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>88.34808259587021</v>
+      </c>
+      <c r="C25" t="n">
+        <v>88.19707563166494</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.3426233205682365</v>
+      </c>
+      <c r="E25" t="n">
+        <v>88.34808259587021</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sub14ex1</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>83.95574356179552</v>
+      </c>
+      <c r="C26" t="n">
+        <v>82.54046879536666</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.5704456083738478</v>
+      </c>
+      <c r="E26" t="n">
+        <v>83.95574356179552</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sub14ex2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>82.8613569321534</v>
+      </c>
+      <c r="C27" t="n">
+        <v>82.51536788026787</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.6515696789235031</v>
+      </c>
+      <c r="E27" t="n">
+        <v>82.8613569321534</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>sub14ex3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>86.46017699115045</v>
+      </c>
+      <c r="C28" t="n">
+        <v>84.98159846436093</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.4617182990419678</v>
+      </c>
+      <c r="E28" t="n">
+        <v>86.46017699115045</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>sub15ex1</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>95.9882005899705</v>
+      </c>
+      <c r="C29" t="n">
+        <v>95.97237483922231</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.1409324539096512</v>
+      </c>
+      <c r="E29" t="n">
+        <v>95.9882005899705</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>sub15ex2</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>93.15668820664538</v>
+      </c>
+      <c r="C30" t="n">
+        <v>93.22212621896622</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.1909778006269031</v>
+      </c>
+      <c r="E30" t="n">
+        <v>93.15668820664538</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>sub15ex3</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>95.16224188790561</v>
+      </c>
+      <c r="C31" t="n">
+        <v>95.02909069897029</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.1556221062466231</v>
+      </c>
+      <c r="E31" t="n">
+        <v>95.16224188790559</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>90.5016796569751</v>
+      </c>
+      <c r="C32" t="n">
+        <v>90.02393898401543</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.2972172011788149</v>
+      </c>
+      <c r="E32" t="n">
+        <v>90.5016796569751</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>3.524123381988782</v>
+      </c>
+      <c r="C33" t="n">
+        <v>3.858330659491744</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.1355950861170081</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3.524123381988782</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>f1_score</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>sub6ex1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>73.17537348939004</v>
+      </c>
+      <c r="C2" t="n">
+        <v>72.79702365390905</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.6333542853593827</v>
+      </c>
+      <c r="E2" t="n">
+        <v>73.17537348939005</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sub6ex2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>76.18837533196654</v>
+      </c>
+      <c r="C3" t="n">
+        <v>76.03728676012173</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5819011015196641</v>
+      </c>
+      <c r="E3" t="n">
+        <v>76.18837533196654</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sub6ex3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>77.15058088737791</v>
+      </c>
+      <c r="C4" t="n">
+        <v>76.65952441080434</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.588161468009154</v>
+      </c>
+      <c r="E4" t="n">
+        <v>77.15058088737791</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sub7ex1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>67.60638067803355</v>
+      </c>
+      <c r="C5" t="n">
+        <v>66.64386604657783</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.7280301744739214</v>
+      </c>
+      <c r="E5" t="n">
+        <v>67.60638067803355</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sub7ex2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>62.80210036419</v>
+      </c>
+      <c r="C6" t="n">
+        <v>62.64734045215262</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.8547167370716731</v>
+      </c>
+      <c r="E6" t="n">
+        <v>62.80210036419</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sub7ex3</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>55.97539771105287</v>
+      </c>
+      <c r="C7" t="n">
+        <v>55.46607971183366</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.9846872399250666</v>
+      </c>
+      <c r="E7" t="n">
+        <v>55.97539771105287</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sub8ex1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>78.27481206584832</v>
+      </c>
+      <c r="C8" t="n">
+        <v>77.00845492821838</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.5194803877248584</v>
+      </c>
+      <c r="E8" t="n">
+        <v>78.27481206584832</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sub8ex2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>83.64388965302467</v>
+      </c>
+      <c r="C9" t="n">
+        <v>83.40108451614476</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.3732309790405755</v>
+      </c>
+      <c r="E9" t="n">
+        <v>83.64388965302469</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sub8ex3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>85.99581311257018</v>
+      </c>
+      <c r="C10" t="n">
+        <v>85.98711042100744</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.3676471432670951</v>
+      </c>
+      <c r="E10" t="n">
+        <v>85.99581311257018</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sub9ex1</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>80.51566190018944</v>
+      </c>
+      <c r="C11" t="n">
+        <v>80.67741485520767</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.4677176573624213</v>
+      </c>
+      <c r="E11" t="n">
+        <v>80.51566190018944</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sub9ex2</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>68.34626597115891</v>
+      </c>
+      <c r="C12" t="n">
+        <v>68.16023864865565</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.7607226590315501</v>
+      </c>
+      <c r="E12" t="n">
+        <v>68.34626597115891</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sub9ex3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>71.62302442062648</v>
+      </c>
+      <c r="C13" t="n">
+        <v>71.48337328087072</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.7354918971657753</v>
+      </c>
+      <c r="E13" t="n">
+        <v>71.62302442062648</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sub10ex1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>60.1876313808943</v>
+      </c>
+      <c r="C14" t="n">
+        <v>59.51788137560168</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.8709068089723587</v>
+      </c>
+      <c r="E14" t="n">
+        <v>60.1876313808943</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sub10ex2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>60.64957309319284</v>
+      </c>
+      <c r="C15" t="n">
+        <v>59.84831760760557</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.924535189072291</v>
+      </c>
+      <c r="E15" t="n">
+        <v>60.64957309319284</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sub10ex3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>56.14823657644098</v>
+      </c>
+      <c r="C16" t="n">
+        <v>55.25884808860909</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.9309013108412424</v>
+      </c>
+      <c r="E16" t="n">
+        <v>56.14823657644096</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>sub11ex1</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>81.72008408377235</v>
+      </c>
+      <c r="C17" t="n">
+        <v>81.6548864031036</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.4572320795307557</v>
+      </c>
+      <c r="E17" t="n">
+        <v>81.72008408377235</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sub11ex2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>77.63328402494832</v>
+      </c>
+      <c r="C18" t="n">
+        <v>76.75427445432562</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.603185295065244</v>
+      </c>
+      <c r="E18" t="n">
+        <v>77.63328402494831</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>sub11ex3</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>85.13568456474536</v>
+      </c>
+      <c r="C19" t="n">
+        <v>84.9555719528424</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.4019875804893672</v>
+      </c>
+      <c r="E19" t="n">
+        <v>85.13568456474538</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>sub12ex1</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>69.6032837654305</v>
+      </c>
+      <c r="C20" t="n">
+        <v>68.1013098033055</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.8173108474661905</v>
+      </c>
+      <c r="E20" t="n">
+        <v>69.6032837654305</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>sub12ex2</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>66.45109386759401</v>
+      </c>
+      <c r="C21" t="n">
+        <v>65.30353692066355</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.8581213607763252</v>
+      </c>
+      <c r="E21" t="n">
+        <v>66.45109386759401</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sub12ex3</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>76.9737627488127</v>
+      </c>
+      <c r="C22" t="n">
+        <v>76.23779800082659</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.6562808928390343</v>
+      </c>
+      <c r="E22" t="n">
+        <v>76.9737627488127</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>sub13ex1</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>66.51580030969126</v>
+      </c>
+      <c r="C23" t="n">
+        <v>65.36133161132484</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.7889941436549028</v>
+      </c>
+      <c r="E23" t="n">
+        <v>66.51580030969126</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sub13ex2</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>74.20764885509391</v>
+      </c>
+      <c r="C24" t="n">
+        <v>74.02653168174777</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.6289542218049368</v>
+      </c>
+      <c r="E24" t="n">
+        <v>74.20764885509391</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sub13ex3</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>62.5742437218315</v>
+      </c>
+      <c r="C25" t="n">
+        <v>61.30936981667924</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.803768094877402</v>
+      </c>
+      <c r="E25" t="n">
+        <v>62.5742437218315</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sub14ex1</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>71.97371949584338</v>
+      </c>
+      <c r="C26" t="n">
+        <v>71.4990734689035</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.7111077819019556</v>
+      </c>
+      <c r="E26" t="n">
+        <v>71.97371949584338</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sub14ex2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>64.9409596968832</v>
+      </c>
+      <c r="C27" t="n">
+        <v>64.3893881711798</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.8461653632422289</v>
+      </c>
+      <c r="E27" t="n">
+        <v>64.9409596968832</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>sub14ex3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>72.35339406050225</v>
+      </c>
+      <c r="C28" t="n">
+        <v>72.12789456960776</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.7075565333167713</v>
+      </c>
+      <c r="E28" t="n">
+        <v>72.35339406050225</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>sub15ex1</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>78.33329008036402</v>
+      </c>
+      <c r="C29" t="n">
+        <v>78.26360894219256</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.5255434001485507</v>
+      </c>
+      <c r="E29" t="n">
+        <v>78.33329008036402</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>sub15ex2</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>88.29877421084957</v>
+      </c>
+      <c r="C30" t="n">
+        <v>88.36070648525079</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.3174889216975619</v>
+      </c>
+      <c r="E30" t="n">
+        <v>88.29877421084957</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>sub15ex3</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>89.17611744046229</v>
+      </c>
+      <c r="C31" t="n">
+        <v>88.77347540417165</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.2741779609505708</v>
+      </c>
+      <c r="E31" t="n">
+        <v>89.17611744046229</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>72.80580858542608</v>
+      </c>
+      <c r="C32" t="n">
+        <v>72.29042008144818</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.6573119838866276</v>
+      </c>
+      <c r="E32" t="n">
+        <v>72.80580858542608</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>9.124539005156802</v>
+      </c>
+      <c r="C33" t="n">
+        <v>9.346971890711115</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.1936332976728984</v>
+      </c>
+      <c r="E33" t="n">
+        <v>9.124539005156803</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>f1_score</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>sub6ex1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>49.54817948252147</v>
+      </c>
+      <c r="C2" t="n">
+        <v>47.00944605206875</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.093492605288823</v>
+      </c>
+      <c r="E2" t="n">
+        <v>49.54817948252148</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sub6ex2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>52.36559139784946</v>
+      </c>
+      <c r="C3" t="n">
+        <v>50.57018559920738</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.076372534036636</v>
+      </c>
+      <c r="E3" t="n">
+        <v>52.36559139784946</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sub6ex3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>56.79945328246784</v>
+      </c>
+      <c r="C4" t="n">
+        <v>55.1631751274962</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.026048503319422</v>
+      </c>
+      <c r="E4" t="n">
+        <v>56.79945328246784</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sub7ex1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>50.07776883883079</v>
+      </c>
+      <c r="C5" t="n">
+        <v>46.53627116667737</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.076316474874814</v>
+      </c>
+      <c r="E5" t="n">
+        <v>50.07776883883079</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sub7ex2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>48.51971037811746</v>
+      </c>
+      <c r="C6" t="n">
+        <v>46.02862131627585</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.102041521171729</v>
+      </c>
+      <c r="E6" t="n">
+        <v>48.51971037811746</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sub7ex3</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>45.72444398307944</v>
+      </c>
+      <c r="C7" t="n">
+        <v>40.78694270519237</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.215337867538134</v>
+      </c>
+      <c r="E7" t="n">
+        <v>45.72444398307944</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sub8ex1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>63.9363662315418</v>
+      </c>
+      <c r="C8" t="n">
+        <v>63.70182759776883</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.7763648202021918</v>
+      </c>
+      <c r="E8" t="n">
+        <v>63.9363662315418</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sub8ex2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>58.51555809306309</v>
+      </c>
+      <c r="C9" t="n">
+        <v>56.88354704770276</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.9822819545865059</v>
+      </c>
+      <c r="E9" t="n">
+        <v>58.51555809306309</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sub8ex3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>57.19227674979887</v>
+      </c>
+      <c r="C10" t="n">
+        <v>55.44203244648924</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.066226274271806</v>
+      </c>
+      <c r="E10" t="n">
+        <v>57.19227674979887</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sub9ex1</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>56.24209551985744</v>
+      </c>
+      <c r="C11" t="n">
+        <v>54.22249671554935</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.060213655233383</v>
+      </c>
+      <c r="E11" t="n">
+        <v>56.24209551985744</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sub9ex2</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>48.57178695317434</v>
+      </c>
+      <c r="C12" t="n">
+        <v>47.18013213630762</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.08008641799291</v>
+      </c>
+      <c r="E12" t="n">
+        <v>48.57178695317434</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sub9ex3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>52.56516059827506</v>
+      </c>
+      <c r="C13" t="n">
+        <v>51.03586354130708</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.086455815037092</v>
+      </c>
+      <c r="E13" t="n">
+        <v>52.56516059827506</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sub10ex1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>45.04511284699695</v>
+      </c>
+      <c r="C14" t="n">
+        <v>40.23475901844889</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.247220480938753</v>
+      </c>
+      <c r="E14" t="n">
+        <v>45.04511284699695</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sub10ex2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>46.54434726944005</v>
+      </c>
+      <c r="C15" t="n">
+        <v>44.86022534031444</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.111646711826324</v>
+      </c>
+      <c r="E15" t="n">
+        <v>46.54434726944005</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sub10ex3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>47.18881651225357</v>
+      </c>
+      <c r="C16" t="n">
+        <v>45.19826178352194</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.146213862299919</v>
+      </c>
+      <c r="E16" t="n">
+        <v>47.18881651225357</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>sub11ex1</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>60.68824124776167</v>
+      </c>
+      <c r="C17" t="n">
+        <v>58.25521175278236</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.8730272352695465</v>
+      </c>
+      <c r="E17" t="n">
+        <v>60.68824124776165</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sub11ex2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>57.5641657799808</v>
+      </c>
+      <c r="C18" t="n">
+        <v>56.01886516740012</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.9695675810178122</v>
+      </c>
+      <c r="E18" t="n">
+        <v>57.5641657799808</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>sub11ex3</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>59.39117120390315</v>
+      </c>
+      <c r="C19" t="n">
+        <v>57.60590975081512</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.9406606713930767</v>
+      </c>
+      <c r="E19" t="n">
+        <v>59.39117120390315</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>sub12ex1</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>54.50877602747429</v>
+      </c>
+      <c r="C20" t="n">
+        <v>52.91875462289937</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.036417228976885</v>
+      </c>
+      <c r="E20" t="n">
+        <v>54.50877602747429</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>sub12ex2</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>53.54086108011315</v>
+      </c>
+      <c r="C21" t="n">
+        <v>51.97569397918441</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.0686019718647</v>
+      </c>
+      <c r="E21" t="n">
+        <v>53.54086108011315</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sub12ex3</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>57.42290158219362</v>
+      </c>
+      <c r="C22" t="n">
+        <v>55.94963097445221</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.9828228563070297</v>
+      </c>
+      <c r="E22" t="n">
+        <v>57.42290158219362</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>sub13ex1</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>46.53500462806772</v>
+      </c>
+      <c r="C23" t="n">
+        <v>41.92144907996392</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.237565499544144</v>
+      </c>
+      <c r="E23" t="n">
+        <v>46.53500462806771</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sub13ex2</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>50.4591735222623</v>
+      </c>
+      <c r="C24" t="n">
+        <v>49.78381384850975</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.034889668226242</v>
+      </c>
+      <c r="E24" t="n">
+        <v>50.4591735222623</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sub13ex3</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>46.80447062690854</v>
+      </c>
+      <c r="C25" t="n">
+        <v>45.06269969020163</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.118100559711456</v>
+      </c>
+      <c r="E25" t="n">
+        <v>46.80447062690854</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sub14ex1</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>58.57939947577402</v>
+      </c>
+      <c r="C26" t="n">
+        <v>57.39719626140423</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1.009641086806854</v>
+      </c>
+      <c r="E26" t="n">
+        <v>58.579399475774</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sub14ex2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>45.42686355418299</v>
+      </c>
+      <c r="C27" t="n">
+        <v>41.89326470192258</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.240119185050328</v>
+      </c>
+      <c r="E27" t="n">
+        <v>45.42686355418299</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>sub14ex3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>44.84554364657134</v>
+      </c>
+      <c r="C28" t="n">
+        <v>38.6265745270807</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1.302739650011063</v>
+      </c>
+      <c r="E28" t="n">
+        <v>44.84554364657134</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>sub15ex1</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>69.92300971461691</v>
+      </c>
+      <c r="C29" t="n">
+        <v>69.11210314331649</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.7139062556127708</v>
+      </c>
+      <c r="E29" t="n">
+        <v>69.92300971461691</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>sub15ex2</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>59.81920258825769</v>
+      </c>
+      <c r="C30" t="n">
+        <v>57.16091926579467</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1.202257542808851</v>
+      </c>
+      <c r="E30" t="n">
+        <v>59.81920258825768</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>sub15ex3</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>77.57653612920527</v>
+      </c>
+      <c r="C31" t="n">
+        <v>76.70328356517273</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.6158748492598534</v>
+      </c>
+      <c r="E31" t="n">
+        <v>77.57653612920527</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>54.06406629815137</v>
+      </c>
+      <c r="C32" t="n">
+        <v>51.84130526417428</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.049750378015968</v>
+      </c>
+      <c r="E32" t="n">
+        <v>54.06406629815137</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>7.59911486304927</v>
+      </c>
+      <c r="C33" t="n">
+        <v>8.490058836766703</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.1515481172979536</v>
+      </c>
+      <c r="E33" t="n">
+        <v>7.59911486304927</v>
       </c>
     </row>
   </sheetData>
